--- a/human_validation/judge/kor/judge_D005_S004_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S004_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,446 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 여기 신시내티의 예술계랑 금융계 사람들 중 몇몇이 저를, 그러니까 제가 어떤 고객을 만나는지, 어디를 가는지 같은 걸 추적하고 있다는 생각을 떨쳐내기가 힘들어서 왔어요. 초대장이나 패널 주제, 심지어 행사에서 누가 제 옆에 앉게 되는지에서도 작은 신호들이 보여요. 그냥 우연일 수도 있다고 스스로 되뇌긴 하는데, 그게 잘 떨쳐지지가 않아서 계속 신경 쓰이네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 본인이 감시당하고 있다는 이런 믿음을, 대부분의 사람들이 믿기 힘들거나 이해하기 어려워할 만한 것이라고 표현하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네, 대부분 사람들이 이해하기 힘들 것 같아요. 소리 내어 말하면 이상하게 들린다는 것도 알아요. 근데 제게는 패턴이 있는 것처럼 느껴져요—받는 초대장이라든가 패널 주제, 아니면 행사에서 누가 제 옆에 앉게 되는지 같은 게요—그리고 그게 제가 누구를 만나는지, 뭘 하고 있는지랑 연결돼 있는 것처럼 느껴져요. 그냥 우연일 수도 있다고 스스로 말해봐도, 그걸 잘 떨쳐내지 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 감시당하고 있다는 이런 믿음을 가진 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 이제 두 달쯤 된 것 같아요. 그때부터 사람들이 제 고객 미팅을 추적하고 그런 식의 신호를 보내고 있다는 느낌이 정말 뚜렷하게 느껴지기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 감시당하고 있다는 이 믿음이 일상 활동이나 인간관계에 영향을 미쳤나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 그래요. 여전히 일은 하고 있는데, 예전 같은 수준은 아니에요. 후속 연락을 놓치거나 고객에게 다시 연락하는 걸 미루게 되면서 사무소 규모가 작아졌어요. 예전에는 관계를 유지하는 데 당연한 부분이었던 공개 패널이나 행사도 몇 개 피하고 있고요. 그러니까 그럭저럭 해나가고는 있는데, 확실히 고객과의 접촉을 얼마나 유지하는지에 영향을 미쳤어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 감시당하고 있다는 이 믿음 때문에 상당한 불안이나 두려움을 느낀 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 그러니까… 어느 정도는요, 네. 항상 무서워서 떨고 있다고는 말 못 하겠는데, 긴장하게는 돼요. 행사에 가거나 사람들을 만나러 갈 때, 그게 뭔가 연결돼 있는 건 아닐까 걱정하기 시작하고, 그게 그걸 피하게 하거나 다시 생각하게 만들어요. 공황이라기보다는 지속적인 불안감에 더 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이런 패턴과 신호들을 생각할 때, 그게 진짜가 아닐 수도 있다고 의심해 보시나요, 아니면 진짜라고 꽤 확신하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 가끔은 의심하긴 해요. 스스로한테, 뭐 초대장이나 패널 주제, 사람들이 어디 앉는지 같은 게 그냥 우연일 수도 있다고 말해요. 근데 그러다가도 너무 딱 맞아떨어지는 방식으로 계속 이어져요, 예술계랑 금융계 사람들이 제가 누구를 만나는지 추적하고 있는 것처럼요. 그러니까… 잠깐은 의심할 수 있는데, 진짜로 떨쳐내지는 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 예술계와 금융계 사람들이 본인을 추적하고 있다는 생각이 실제로 일어날 수 있는 일이라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네, 일어날 수 있는 일이라고 생각해요. 그러니까, 여기 신시내티는 실제로 존재하는 커뮤니티고, 사람들이 서로 얘기하고 알고 지내요. 누군가 초대장이나 패널 주제, 아니면 행사에서 자리 배치 같은 걸 통해 제가 누구를 만나는지 계속 파악하고 있다는 게 불가능하게 느껴지지는 않아요. 그중 일부는 우연일 수도 있다는 건 알지만, 그냥 무시하기엔 너무 구체적으로 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 예술계와 금융계 사람들이 실제로 본인을 추적하고 있다고 얼마나 확신하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 꽤 확신하는 편이에요… 100퍼센트는 아니에요, 가끔은 우연일 수도 있다고 스스로 말하는 순간들이 있으니까요. 근데 대부분은 저한테 진짜처럼 느껴져요. 초대장이 오는 방식이라든가, 패널 주제, 심지어 행사에서 제 옆에 누가 앉는지까지—그 사람들이 제가 누구를 만나는지 조용히 추적하고 있는 것처럼 느껴져요. 그걸 떨쳐내기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 본인을 추적하는 사람들에게 논리적이거나 이해할 만한 동기가 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 그러니까… 네, 저한테는 이해가 돼요. 그 예술계랑 금융계 안에서는 사람들이 서로 알고, 제가 누구를 만나는지가 그 사람들한테 중요할 수 있어요—고객이라든가 인맥 같은 거요. 그러니까 만약 그 사람들이 조용히 추적하려 한다면, 이유가 있을 수 있다고 봐요. 제가 너무 확대해석하는 것처럼 들릴 수도 있다는 건 아는데, 초대장이랑 패널 주제랑 좌석 배치가 계속 맞아떨어지는 걸 보면, 뭔가 목적이 있는 것처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 초대장, 패널 주제, 좌석 배치를 통해 사람들이 본인을 추적하고 있다는 생각이 대부분의 사람들이 이상하거나 이해하기 어렵다고 여길 만한 믿음이라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네… 대부분 사람들이 이해하기 힘들 것 같아요. 그러니까, 제가 초대장이나 패널 주제, 아니면 제 옆에 앉는 사람들이 신호라고 소리 내어 말하면, 이상하게 들린다는 걸 알아요. 근데 저한테는 여전히 연관돼 있는 것처럼 느껴져요, 무시하기에는 너무 구체적으로 계속 맞아떨어지는 것처럼요. 우연일 수도 있다고 스스로 말해봐도, 진짜로 떨쳐내지는 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 사람들이 본인을 추적하고 있다고 믿지 않았던 시기가, 짧게라도 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 의심하는 순간들은 있어요, 네. 초대장이나 좌석 배치 같은 게 그냥 우연일 수도 있다고 스스로 말해보기도 해요. 근데 완전히 그걸 믿지 않았던 진짜 시기가 있었던 것 같지는 않아요. 계속 연관된 것처럼 느껴지는 쪽으로 돌아오고, 그걸 진짜로 떨쳐내지는 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 이런 특정한 방식들로 사람들이 본인을 추적하고 있다는 믿음이 본인에게는 정상적이고 합리적으로 들린다고 표현하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 저한테는 합리적으로 느껴져요, 네. 그러니까, 다른 사람한테 설명하면 아마 이상하게 들릴 거라는 건 알아요. 근데 제 머릿속에서는, 특정 초대장이 나오는 방식이라든가 패널 주제가 뭔가랑 맞아떨어지는 거라든가, 행사에서 같은 부류의 사람들이 제 곁에 있게 되는 거라든가… 그게 그냥 무시하기에는 너무 구체적으로 느껴져요. 그러니까 우연일 수도 있다고 스스로 말할 수는 있는데, 그 사람들이 어떻게든 저를 추적하고 있다는 믿음을 진짜로 떨쳐내지는 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 사람들이 본인을 추적하고 있다는 이 믿음 때문에 개인적인 인간관계에 변화가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네, 어느 정도요. 여전히 일은 유지하고 있어요, 조각조각이긴 해도요. 근데 사람들에 대한 예전 같은 에너지는 없어요. 고객 후속 연락을 필요 이상으로 오래 미뤄두고, 일 밖에서는 재즈 나이트나 픽업 농구도 빠지고 있어요.
+친구들이 무슨 일이냐고 물으면 보통 짧게 대답하고 말아요. 그 사람들을 신경 안 쓴다는 건 아닌데… 얘기하는 게 그냥 필요 이상으로 힘든 일처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 초대장, 패널 주제, 좌석 배치를 통해 받고 있다고 느끼는 신호들을 다른 사람들이 논리적으로 이해하거나 설명할 수 있을 거라고 표현하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 그 패턴을 누군가한테 설명은 할 수 있을 것 같아요, 왜 초대장이나 패널 주제가 제가 누굴 만나는지랑 연결돼 있다고 느껴지는지요. 근데 그 사람들이 그걸 논리적이라고 볼지는… 잘 모르겠어요. 다른 사람들한테는 그냥 우연으로 들릴 거라는 건 알아요.
+근데 저한테는 너무 구체적으로 느껴져요. 정상적인 설명이 있을 거라고 스스로 말해봐도, 그걸 진짜로 떨쳐내지는 못해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 며칠 이상, 사람들이 본인을 추적하고 있다고 생각하지 않았던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 딱히 없어요. 이제 두 달째 꽤 꾸준하게 이어지고 있어요. 정신이 딴 데 팔려서 그 생각을 안 하는 순간들은 있을 수도 있는데, 며칠 이상 그게 안 돌아온 적은 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 초대장, 패널 주제, 좌석 배치를 통해 사람들이 본인을 추적하고 있다는 생각을 기이하거나 현실에서 일어날 수 없는 일이라고 표현하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 불가능하다고 부르지는 않을 것 같아요. 그러니까, 사람들이 누가 누구를 만나는지 추적할 수는 있잖아요, 특히 서로 다 아는 금융계나 예술계 같은 곳에서는요. 아마 이상하게 들릴 부분은 초대장이나 좌석, 패널 주제가 신호처럼 느껴진다는 거겠죠.
+다른 사람한테는 현실적으로 안 들릴 수도 있다는 건 아는데, 그냥 우연일 수도 있다고 스스로 말해보기도 해요. 근데 저한테는 너무 연관돼 있어서 그냥 넘길 수가 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 일주일 이상, 사람들이 본인을 추적하고 있다는 믿음을 완전히 멈췄던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 아니요, 완전히 안 믿었던 한 주가 통째로 있었던 것 같지는 않아요.
+스스로를 설득해서, 아 그냥 초대장이나 좌석 같은 게 우연일 수도 있다고 생각하는 순간들은 있어요. 근데 그러다가도 그 예술계나 금융계에서 다른 일이 일어나면 다시 연관된 것처럼 느껴져요. 그러니까 완전히 사라지지는 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 본인이 이런 신호들을 잘못 해석하고 있고 사람들이 실제로 본인을 추적하는 게 아닐 가능성이 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 네, 가능성이 있다고 생각해요. 그러니까, 초대장이나 제 옆에 앉는 사람, 아니면 패널 주제를 너무 확대해석하고 있는 건 아닌가 스스로한테 말해볼 수 있어요. 다 우연일 수도 있죠.
+근데 진짜로 떨쳐내지는 못해요. 여전히 여기 신시내티의 예술계랑 금융계에 있는 어떤 사람들이 제가 만나는 고객을 조용히 추적하고 작은 신호를 보내고 있는 것처럼 느껴져요. 그러니까 제가 잘못 해석하고 있을 수도 있다는 건 알지만, 대부분은 그렇게 느껴지지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 다른 사람들도 본인이 감시당하고 있다는 믿음에 동의할 거라고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 아마 대부분은 안 그럴 거예요. 많은 사람들이 제가 너무 확대해석한다고, 초대장이나 패널 주제나 사람들 자리 배치 같은 건 그냥 평범한 행사 진행일 뿐이라고 할 것 같아요.
+근데 저한테는 여전히 연관돼 있는 것처럼 느껴져요, 특히 여기 예술계랑 금융계의 특정 사람들이랑요. 그러니까 다른 사람들은 동의 안 할 수도 있다는 건 알지만, 여전히 그걸 떨쳐내기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 본인이 받고 있다고 믿는 신호들이 사람들이 본인을 추적하고 있다는 것 외에 다른 걸로 설명될 수 있다고 생각하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 그러니까, 네, 그럴 수 있어요. 초대장이나 패널 주제, 행사에서 사람들이 어디 앉는지 같은 게 그냥 우연이거나 평범한 네트워킹일 수도 있다는 건 이해할 수 있어요.
+근데 그게 여기 신시내티의 같은 예술계랑 금융계 사람들을 중심으로 계속 일어나고, 제가 만난 고객들이랑 맞아떨어지면, 그 설명을 받아들이기가 힘들어요. 마음 한편으로는 다른 이유가 있을 수도 있다는 걸 알지만, 여전히 그 사람들이 어떻게든 저를 추적하고 있는 것처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현병 (D005)
 인구통계: 성별 남성 / 나이 32 / 직업상태 personal financial advisor / 최종학력 학사
@@ -575,495 +1006,31 @@
 증상 지속 기간: 2 years and 2 months
 추가 요건: 
 주호소 증상 코드: S019
-배경 서술: 브렌트 이글린이 처음으로 큰 직업적 인정을 받은 것은 신시내티의 한 예술 비영리단체가 그가 젊은 흑인 예술가와 사업가들이 장기 재정 계획을 세우도록 도운 공로를 기려 그를 표창하면서였고, 이는 그의 부티크 사무소에 새로운 고객과 대중의 관심을 가져다주었다. 이후 2년 2개월에 걸쳐, 처음에는 성공에서 오는 압박처럼 보였던 것이 점차 전문 및 문화 네트워크에 대한 고정된 믿음의 패턴으로 굳어졌고, 그의 평소 따뜻함과 말의 활기, 그리고 농구, 재즈 나이트, 여행 계획, 요리에 대한 관심 참여도 눈에 띄게 줄어들었다. 장애는 경미한 수준에 머물렀지만 임상적으로 의미가 있었다. 그는 여전히 일부 고객을 유지했지만 후속 연락을 놓치고, 업무 범위를 좁혔으며, 대중 앞에서의 발표가 점점 어려워졌다. 브렌트는 자신의 일기를 다시 살펴보다가 이러한 변화가 지속적이고 악화되고 있으며, 자신의 생계와 예술 커뮤니티 안에서의 역할 모두를 위협하기 시작했다는 것을 깨닫고 스스로 정신과 진료를 받으러 왔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 여기 신시내티의 예술계랑 금융계 사람들 중 몇몇이 저를, 그러니까 제가 어떤 고객을 만나는지, 어디를 가는지 같은 걸 추적하고 있다는 생각을 떨쳐내기가 힘들어서 왔어요. 초대장이나 패널 주제, 심지어 행사에서 누가 제 옆에 앉게 되는지에서도 작은 신호들이 보여요. 그냥 우연일 수도 있다고 스스로 되뇌긴 하는데, 그게 잘 떨쳐지지가 않아서 계속 신경 쓰이네요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 본인이 감시당하고 있다는 이런 믿음을, 대부분의 사람들이 믿기 힘들거나 이해하기 어려워할 만한 것이라고 표현하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네, 대부분 사람들이 이해하기 힘들 것 같아요. 소리 내어 말하면 이상하게 들린다는 것도 알아요. 근데 제게는 패턴이 있는 것처럼 느껴져요—받는 초대장이라든가 패널 주제, 아니면 행사에서 누가 제 옆에 앉게 되는지 같은 게요—그리고 그게 제가 누구를 만나는지, 뭘 하고 있는지랑 연결돼 있는 것처럼 느껴져요. 그냥 우연일 수도 있다고 스스로 말해봐도, 그걸 잘 떨쳐내지 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 감시당하고 있다는 이런 믿음을 가진 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 이제 두 달쯤 된 것 같아요. 그때부터 사람들이 제 고객 미팅을 추적하고 그런 식의 신호를 보내고 있다는 느낌이 정말 뚜렷하게 느껴지기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 감시당하고 있다는 이 믿음이 일상 활동이나 인간관계에 영향을 미쳤나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 그래요. 여전히 일은 하고 있는데, 예전 같은 수준은 아니에요. 후속 연락을 놓치거나 고객에게 다시 연락하는 걸 미루게 되면서 사무소 규모가 작아졌어요. 예전에는 관계를 유지하는 데 당연한 부분이었던 공개 패널이나 행사도 몇 개 피하고 있고요. 그러니까 그럭저럭 해나가고는 있는데, 확실히 고객과의 접촉을 얼마나 유지하는지에 영향을 미쳤어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 감시당하고 있다는 이 믿음 때문에 상당한 불안이나 두려움을 느낀 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 그러니까… 어느 정도는요, 네. 항상 무서워서 떨고 있다고는 말 못 하겠는데, 긴장하게는 돼요. 행사에 가거나 사람들을 만나러 갈 때, 그게 뭔가 연결돼 있는 건 아닐까 걱정하기 시작하고, 그게 그걸 피하게 하거나 다시 생각하게 만들어요. 공황이라기보다는 지속적인 불안감에 더 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이런 패턴과 신호들을 생각할 때, 그게 진짜가 아닐 수도 있다고 의심해 보시나요, 아니면 진짜라고 꽤 확신하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 가끔은 의심하긴 해요. 스스로한테, 뭐 초대장이나 패널 주제, 사람들이 어디 앉는지 같은 게 그냥 우연일 수도 있다고 말해요. 근데 그러다가도 너무 딱 맞아떨어지는 방식으로 계속 이어져요, 예술계랑 금융계 사람들이 제가 누구를 만나는지 추적하고 있는 것처럼요. 그러니까… 잠깐은 의심할 수 있는데, 진짜로 떨쳐내지는 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 예술계와 금융계 사람들이 본인을 추적하고 있다는 생각이 실제로 일어날 수 있는 일이라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네, 일어날 수 있는 일이라고 생각해요. 그러니까, 여기 신시내티는 실제로 존재하는 커뮤니티고, 사람들이 서로 얘기하고 알고 지내요. 누군가 초대장이나 패널 주제, 아니면 행사에서 자리 배치 같은 걸 통해 제가 누구를 만나는지 계속 파악하고 있다는 게 불가능하게 느껴지지는 않아요. 그중 일부는 우연일 수도 있다는 건 알지만, 그냥 무시하기엔 너무 구체적으로 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 예술계와 금융계 사람들이 실제로 본인을 추적하고 있다고 얼마나 확신하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 꽤 확신하는 편이에요… 100퍼센트는 아니에요, 가끔은 우연일 수도 있다고 스스로 말하는 순간들이 있으니까요. 근데 대부분은 저한테 진짜처럼 느껴져요. 초대장이 오는 방식이라든가, 패널 주제, 심지어 행사에서 제 옆에 누가 앉는지까지—그 사람들이 제가 누구를 만나는지 조용히 추적하고 있는 것처럼 느껴져요. 그걸 떨쳐내기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 본인을 추적하는 사람들에게 논리적이거나 이해할 만한 동기가 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 그러니까… 네, 저한테는 이해가 돼요. 그 예술계랑 금융계 안에서는 사람들이 서로 알고, 제가 누구를 만나는지가 그 사람들한테 중요할 수 있어요—고객이라든가 인맥 같은 거요. 그러니까 만약 그 사람들이 조용히 추적하려 한다면, 이유가 있을 수 있다고 봐요. 제가 너무 확대해석하는 것처럼 들릴 수도 있다는 건 아는데, 초대장이랑 패널 주제랑 좌석 배치가 계속 맞아떨어지는 걸 보면, 뭔가 목적이 있는 것처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 초대장, 패널 주제, 좌석 배치를 통해 사람들이 본인을 추적하고 있다는 생각이 대부분의 사람들이 이상하거나 이해하기 어렵다고 여길 만한 믿음이라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네… 대부분 사람들이 이해하기 힘들 것 같아요. 그러니까, 제가 초대장이나 패널 주제, 아니면 제 옆에 앉는 사람들이 신호라고 소리 내어 말하면, 이상하게 들린다는 걸 알아요. 근데 저한테는 여전히 연관돼 있는 것처럼 느껴져요, 무시하기에는 너무 구체적으로 계속 맞아떨어지는 것처럼요. 우연일 수도 있다고 스스로 말해봐도, 진짜로 떨쳐내지는 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 사람들이 본인을 추적하고 있다고 믿지 않았던 시기가, 짧게라도 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 의심하는 순간들은 있어요, 네. 초대장이나 좌석 배치 같은 게 그냥 우연일 수도 있다고 스스로 말해보기도 해요. 근데 완전히 그걸 믿지 않았던 진짜 시기가 있었던 것 같지는 않아요. 계속 연관된 것처럼 느껴지는 쪽으로 돌아오고, 그걸 진짜로 떨쳐내지는 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 이런 특정한 방식들로 사람들이 본인을 추적하고 있다는 믿음이 본인에게는 정상적이고 합리적으로 들린다고 표현하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 저한테는 합리적으로 느껴져요, 네. 그러니까, 다른 사람한테 설명하면 아마 이상하게 들릴 거라는 건 알아요. 근데 제 머릿속에서는, 특정 초대장이 나오는 방식이라든가 패널 주제가 뭔가랑 맞아떨어지는 거라든가, 행사에서 같은 부류의 사람들이 제 곁에 있게 되는 거라든가… 그게 그냥 무시하기에는 너무 구체적으로 느껴져요. 그러니까 우연일 수도 있다고 스스로 말할 수는 있는데, 그 사람들이 어떻게든 저를 추적하고 있다는 믿음을 진짜로 떨쳐내지는 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 사람들이 본인을 추적하고 있다는 이 믿음 때문에 개인적인 인간관계에 변화가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네, 어느 정도요. 여전히 일은 유지하고 있어요, 조각조각이긴 해도요. 근데 사람들에 대한 예전 같은 에너지는 없어요. 고객 후속 연락을 필요 이상으로 오래 미뤄두고, 일 밖에서는 재즈 나이트나 픽업 농구도 빠지고 있어요.
-친구들이 무슨 일이냐고 물으면 보통 짧게 대답하고 말아요. 그 사람들을 신경 안 쓴다는 건 아닌데… 얘기하는 게 그냥 필요 이상으로 힘든 일처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 초대장, 패널 주제, 좌석 배치를 통해 받고 있다고 느끼는 신호들을 다른 사람들이 논리적으로 이해하거나 설명할 수 있을 거라고 표현하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 그 패턴을 누군가한테 설명은 할 수 있을 것 같아요, 왜 초대장이나 패널 주제가 제가 누굴 만나는지랑 연결돼 있다고 느껴지는지요. 근데 그 사람들이 그걸 논리적이라고 볼지는… 잘 모르겠어요. 다른 사람들한테는 그냥 우연으로 들릴 거라는 건 알아요.
-근데 저한테는 너무 구체적으로 느껴져요. 정상적인 설명이 있을 거라고 스스로 말해봐도, 그걸 진짜로 떨쳐내지는 못해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 며칠 이상, 사람들이 본인을 추적하고 있다고 생각하지 않았던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 딱히 없어요. 이제 두 달째 꽤 꾸준하게 이어지고 있어요. 정신이 딴 데 팔려서 그 생각을 안 하는 순간들은 있을 수도 있는데, 며칠 이상 그게 안 돌아온 적은 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 초대장, 패널 주제, 좌석 배치를 통해 사람들이 본인을 추적하고 있다는 생각을 기이하거나 현실에서 일어날 수 없는 일이라고 표현하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 불가능하다고 부르지는 않을 것 같아요. 그러니까, 사람들이 누가 누구를 만나는지 추적할 수는 있잖아요, 특히 서로 다 아는 금융계나 예술계 같은 곳에서는요. 아마 이상하게 들릴 부분은 초대장이나 좌석, 패널 주제가 신호처럼 느껴진다는 거겠죠.
-다른 사람한테는 현실적으로 안 들릴 수도 있다는 건 아는데, 그냥 우연일 수도 있다고 스스로 말해보기도 해요. 근데 저한테는 너무 연관돼 있어서 그냥 넘길 수가 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 일주일 이상, 사람들이 본인을 추적하고 있다는 믿음을 완전히 멈췄던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 아니요, 완전히 안 믿었던 한 주가 통째로 있었던 것 같지는 않아요.
-스스로를 설득해서, 아 그냥 초대장이나 좌석 같은 게 우연일 수도 있다고 생각하는 순간들은 있어요. 근데 그러다가도 그 예술계나 금융계에서 다른 일이 일어나면 다시 연관된 것처럼 느껴져요. 그러니까 완전히 사라지지는 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 본인이 이런 신호들을 잘못 해석하고 있고 사람들이 실제로 본인을 추적하는 게 아닐 가능성이 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 네, 가능성이 있다고 생각해요. 그러니까, 초대장이나 제 옆에 앉는 사람, 아니면 패널 주제를 너무 확대해석하고 있는 건 아닌가 스스로한테 말해볼 수 있어요. 다 우연일 수도 있죠.
-근데 진짜로 떨쳐내지는 못해요. 여전히 여기 신시내티의 예술계랑 금융계에 있는 어떤 사람들이 제가 만나는 고객을 조용히 추적하고 작은 신호를 보내고 있는 것처럼 느껴져요. 그러니까 제가 잘못 해석하고 있을 수도 있다는 건 알지만, 대부분은 그렇게 느껴지지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 다른 사람들도 본인이 감시당하고 있다는 믿음에 동의할 거라고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 아마 대부분은 안 그럴 거예요. 많은 사람들이 제가 너무 확대해석한다고, 초대장이나 패널 주제나 사람들 자리 배치 같은 건 그냥 평범한 행사 진행일 뿐이라고 할 것 같아요.
-근데 저한테는 여전히 연관돼 있는 것처럼 느껴져요, 특히 여기 예술계랑 금융계의 특정 사람들이랑요. 그러니까 다른 사람들은 동의 안 할 수도 있다는 건 알지만, 여전히 그걸 떨쳐내기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 본인이 받고 있다고 믿는 신호들이 사람들이 본인을 추적하고 있다는 것 외에 다른 걸로 설명될 수 있다고 생각하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 그러니까, 네, 그럴 수 있어요. 초대장이나 패널 주제, 행사에서 사람들이 어디 앉는지 같은 게 그냥 우연이거나 평범한 네트워킹일 수도 있다는 건 이해할 수 있어요.
-근데 그게 여기 신시내티의 같은 예술계랑 금융계 사람들을 중심으로 계속 일어나고, 제가 만난 고객들이랑 맞아떨어지면, 그 설명을 받아들이기가 힘들어요. 마음 한편으로는 다른 이유가 있을 수도 있다는 걸 알지만, 여전히 그 사람들이 어떻게든 저를 추적하고 있는 것처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 브렌트 이글린이 처음으로 큰 직업적 인정을 받은 것은 신시내티의 한 예술 비영리단체가 그가 젊은 흑인 예술가와 사업가들이 장기 재정 계획을 세우도록 도운 공로를 기려 그를 표창하면서였고, 이는 그의 부티크 사무소에 새로운 고객과 대중의 관심을 가져다주었다. 이후 2년 2개월에 걸쳐, 처음에는 성공에서 오는 압박처럼 보였던 것이 점차 전문 및 문화 네트워크에 대한 고정된 믿음의 패턴으로 굳어졌고, 그의 평소 따뜻함과 말의 활기, 그리고 농구, 재즈 나이트, 여행 계획, 요리에 대한 관심 참여도 눈에 띄게 줄어들었다. 장애는 경미한 수준에 머물렀지만 임상적으로 의미가 있었다. 그는 여전히 일부 고객을 유지했지만 후속 연락을 놓치고, 업무 범위를 좁혔으며, 대중 앞에서의 발표가 점점 어려워졌다. 브렌트는 자신의 일기를 다시 살펴보다가 이러한 변화가 지속적이고 악화되고 있으며, 자신의 생계와 예술 커뮤니티 안에서의 역할 모두를 위협하기 시작했다는 것을 깨닫고 스스로 정신과 진료를 받으러 왔다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 특정공포증 (D012); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
-  누락: 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.</t>
+          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D005_S004_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S004_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -992,6 +992,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1026,11 +1031,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D005_S004_P003__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D005_S004_P003__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1141</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1141</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
